--- a/docs/oc-regiones/articulos-de-escritorio-y-papeleria/magallanes.xlsx
+++ b/docs/oc-regiones/articulos-de-escritorio-y-papeleria/magallanes.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M151"/>
+  <dimension ref="A1:M160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1057402-25393-CM25</t>
+          <t>1057402-25392-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+          <t>LIBRERIA</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>78.307.990-9</t>
+          <t>76.567.094-2</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>997.73</v>
+        <v>1391.49</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1057402-25392-CM25</t>
+          <t>1057402-25393-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>LIBRERIA</t>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>76.567.094-2</t>
+          <t>78.307.990-9</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>1391.49</v>
+        <v>997.73</v>
       </c>
     </row>
     <row r="4">
@@ -1307,7 +1307,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1540-2041-CM25</t>
+          <t>1038-226-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>61.607.904-2</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PTO NATALES</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>LIBRERIA</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.567.094-2</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>5612.03</v>
+        <v>731.7</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1038-226-CM25</t>
+          <t>1540-2041-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1393,12 +1393,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.607.904-2</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PTO NATALES</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1408,12 +1408,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>LIBRERIA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>76.567.094-2</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>731.7</v>
+        <v>5612.03</v>
       </c>
     </row>
     <row r="17">
@@ -1490,7 +1490,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>5394-567-CM25</t>
+          <t>5147-278-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1515,12 +1515,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>71.133.700-8</t>
+          <t>69.251.600-1</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE MAGALLANES</t>
+          <t>ILUSTRE MUNICIPALIDAD DE TIMAUKEL</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>2357.43</v>
+        <v>2552.1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>5147-278-CM25</t>
+          <t>5394-567-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>69.251.600-1</t>
+          <t>71.133.700-8</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE TIMAUKEL</t>
+          <t>UNIVERSIDAD DE MAGALLANES</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>2552.1</v>
+        <v>2357.43</v>
       </c>
     </row>
     <row r="20">
@@ -1673,7 +1673,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2354-428-CM25</t>
+          <t>855-269-CM25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1698,12 +1698,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>69.250.200-0</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUNTA ARENAS</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>LIBRERIA</t>
+          <t>IVÁN DAMIR STIPICIC MATIC</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>76.567.094-2</t>
+          <t>8.588.169-8</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>746.3200000000001</v>
+        <v>730.6</v>
       </c>
     </row>
     <row r="22">
@@ -1795,7 +1795,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>855-269-CM25</t>
+          <t>2354-428-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1820,12 +1820,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>69.250.200-0</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>I MUNICIPALIDAD DE PUNTA ARENAS</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>IVÁN DAMIR STIPICIC MATIC</t>
+          <t>LIBRERIA</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>8.588.169-8</t>
+          <t>76.567.094-2</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -1850,13 +1850,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>730.6</v>
+        <v>746.3200000000001</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>5147-298-CM25</t>
+          <t>2348-1545-CM25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1876,17 +1876,17 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>69.251.600-1</t>
+          <t>69.250.200-0</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE TIMAUKEL</t>
+          <t>I MUNICIPALIDAD DE PUNTA ARENAS</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1896,12 +1896,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>IVÁN DAMIR STIPICIC MATIC</t>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>8.588.169-8</t>
+          <t>78.307.990-9</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -1911,13 +1911,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>725.21</v>
+        <v>720.16</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2348-1545-CM25</t>
+          <t>5147-298-CM25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1937,17 +1937,17 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>69.250.200-0</t>
+          <t>69.251.600-1</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUNTA ARENAS</t>
+          <t>ILUSTRE MUNICIPALIDAD DE TIMAUKEL</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+          <t>IVÁN DAMIR STIPICIC MATIC</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>78.307.990-9</t>
+          <t>8.588.169-8</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -1972,13 +1972,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>720.16</v>
+        <v>725.21</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>874750-435-CM25</t>
+          <t>935-6085-CM25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2003,12 +2003,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>61.607.903-4</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD MAGALLANES</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>MARANGUNIC HERMANOS LIMITADA</t>
+          <t>IVÁN DAMIR STIPICIC MATIC</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>80.586.800-7</t>
+          <t>8.588.169-8</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -2033,13 +2033,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>720.97</v>
+        <v>3102.31</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>935-6085-CM25</t>
+          <t>874750-435-CM25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2064,12 +2064,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>61.607.903-4</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>SERVICIO DE SALUD MAGALLANES</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2079,12 +2079,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>IVÁN DAMIR STIPICIC MATIC</t>
+          <t>MARANGUNIC HERMANOS LIMITADA</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>8.588.169-8</t>
+          <t>80.586.800-7</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -2094,13 +2094,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>3102.31</v>
+        <v>720.97</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1057402-36793-CM25</t>
+          <t>874750-440-CM25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2125,12 +2125,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>61.607.903-4</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>SERVICIO DE SALUD MAGALLANES</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+          <t>IVÁN DAMIR STIPICIC MATIC</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>78.307.990-9</t>
+          <t>8.588.169-8</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -2155,13 +2155,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>723.41</v>
+        <v>727.3099999999999</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>874750-440-CM25</t>
+          <t>1057402-36793-CM25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>61.607.903-4</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD MAGALLANES</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2201,12 +2201,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>IVÁN DAMIR STIPICIC MATIC</t>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>8.588.169-8</t>
+          <t>78.307.990-9</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>727.3099999999999</v>
+        <v>723.41</v>
       </c>
     </row>
     <row r="30">
@@ -2496,7 +2496,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Servicio Nacional de Pesca y Acuicultura</t>
+          <t>SERV NACIONAL DE PESCA</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACION TECNICA ESTATAL DE MAGALLANES</t>
+          <t>CENTRO DE FORMACION TECNICA ESTATAL DE MAGALLANES Y ANTARTICA CHILENA</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACION TECNICA ESTATAL DE MAGALLANES</t>
+          <t>CENTRO DE FORMACION TECNICA ESTATAL DE MAGALLANES Y ANTARTICA CHILENA</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2740,7 +2740,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>DEPTO BIENESTAR SOCIAL (M) 3RA ZONA NAVA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2771,7 +2771,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1347-75-CM25</t>
+          <t>3130-4339-CM25</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2796,12 +2796,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>61.002.492-0</t>
+          <t>61.102.029-5</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>REG CIVIL E IDENT PUNTA ARENAS</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+          <t>LIBRERIA</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>78.307.990-9</t>
+          <t>76.567.094-2</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -2826,13 +2826,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>791.55</v>
+        <v>1339.96</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>3130-4339-CM25</t>
+          <t>1347-75-CM25</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>61.102.029-5</t>
+          <t>61.002.492-0</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>HOSPITAL NAVAL CIRUJANO GUZMAN DE MAGALL</t>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2872,12 +2872,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>LIBRERIA</t>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>76.567.094-2</t>
+          <t>78.307.990-9</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>1339.96</v>
+        <v>791.55</v>
       </c>
     </row>
     <row r="41">
@@ -2923,7 +2923,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACION TECNICA ESTATAL DE MAGALLANES</t>
+          <t>CENTRO DE FORMACION TECNICA ESTATAL DE MAGALLANES Y ANTARTICA CHILENA</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACION TECNICA ESTATAL DE MAGALLANES</t>
+          <t>CENTRO DE FORMACION TECNICA ESTATAL DE MAGALLANES Y ANTARTICA CHILENA</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3015,7 +3015,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>855-258-CM25</t>
+          <t>855-259-CM25</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3070,13 +3070,13 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>1464.93</v>
+        <v>9176.809999999999</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>855-259-CM25</t>
+          <t>855-258-CM25</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>9176.809999999999</v>
+        <v>1464.93</v>
       </c>
     </row>
     <row r="45">
@@ -3167,7 +3167,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>HOSPITAL NAVAL CIRUJANO GUZMAN DE MAGALL</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3228,7 +3228,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Subsecretaria de las Culturas y las Artes Región de Magallanes y la Antartica</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3320,7 +3320,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2019-155-CM25</t>
+          <t>2019-156-CM25</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>JOSÉ HERMINIO BARRIENTOS BARRIENTOS</t>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>7.560.370-3</t>
+          <t>78.307.990-9</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
@@ -3375,13 +3375,13 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>836.8200000000001</v>
+        <v>1932.63</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2019-154-CM25</t>
+          <t>2019-155-CM25</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3421,12 +3421,12 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+          <t>JOSÉ HERMINIO BARRIENTOS BARRIENTOS</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>78.307.990-9</t>
+          <t>7.560.370-3</t>
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
@@ -3436,13 +3436,13 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>1523.61</v>
+        <v>836.8200000000001</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>1057402-43526-CM25</t>
+          <t>2019-154-CM25</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3462,17 +3462,17 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>60.511.122-k</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE ÚLTIMA ESPERANZA</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3497,13 +3497,13 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>807.37</v>
+        <v>1523.61</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2019-156-CM25</t>
+          <t>1057402-43526-CM25</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>60.511.122-k</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE ÚLTIMA ESPERANZA</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3558,13 +3558,13 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>1932.63</v>
+        <v>807.37</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2019-162-CM25</t>
+          <t>1347-79-CM25</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3589,12 +3589,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>60.511.122-k</t>
+          <t>61.002.492-0</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE ÚLTIMA ESPERANZA</t>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3619,13 +3619,13 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>5573.57</v>
+        <v>2305.34</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>5394-857-CM25</t>
+          <t>2019-158-CM25</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3645,17 +3645,17 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>71.133.700-8</t>
+          <t>60.511.122-k</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE MAGALLANES</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE ÚLTIMA ESPERANZA</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3680,13 +3680,13 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>1668.18</v>
+        <v>1679.26</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>1347-79-CM25</t>
+          <t>3268-927-CM25</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3711,12 +3711,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>61.002.492-0</t>
+          <t>61.103.021-5</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>REG CIVIL E IDENT PUNTA ARENAS</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+          <t>LIBRERIA</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>78.307.990-9</t>
+          <t>76.567.094-2</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
@@ -3741,13 +3741,13 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>2305.34</v>
+        <v>8527.690000000001</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2019-158-CM25</t>
+          <t>3268-926-CM25</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3767,17 +3767,17 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>60.511.122-k</t>
+          <t>61.103.021-5</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE ÚLTIMA ESPERANZA</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3802,13 +3802,13 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>1679.26</v>
+        <v>2418.26</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>3268-927-CM25</t>
+          <t>2019-162-CM25</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>61.103.021-5</t>
+          <t>60.511.122-k</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>IVª Brigada Aérea</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE ÚLTIMA ESPERANZA</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>LIBRERIA</t>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>76.567.094-2</t>
+          <t>78.307.990-9</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
@@ -3863,13 +3863,13 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>8527.690000000001</v>
+        <v>5573.57</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>3268-926-CM25</t>
+          <t>5394-857-CM25</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>61.103.021-5</t>
+          <t>71.133.700-8</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>IVª Brigada Aérea</t>
+          <t>UNIVERSIDAD DE MAGALLANES</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3924,7 +3924,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>2418.26</v>
+        <v>1668.18</v>
       </c>
     </row>
     <row r="58">
@@ -4265,7 +4265,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Instituto de Prevision Social</t>
+          <t>INSTITUTO DE PREVISION SOCIAL</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4509,7 +4509,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4601,7 +4601,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>3617-2-CM26</t>
+          <t>5338-31-CM26</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4626,12 +4626,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>71.133.700-8</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>UNIVERSIDAD DE MAGALLANES</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4641,12 +4641,12 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>78.307.990-9</t>
         </is>
       </c>
       <c r="K69" t="inlineStr"/>
@@ -4656,13 +4656,13 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>1392.72</v>
+        <v>14311.5</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>5338-31-CM26</t>
+          <t>3617-2-CM26</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4687,12 +4687,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>71.133.700-8</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE MAGALLANES</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4702,12 +4702,12 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>78.307.990-9</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K70" t="inlineStr"/>
@@ -4717,7 +4717,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>14311.5</v>
+        <v>1392.72</v>
       </c>
     </row>
     <row r="71">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XII ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>CENTRO DE ABASTECIMIENTO (M)</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -4906,7 +4906,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>3166-35-CM26</t>
+          <t>3166-33-CM26</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4936,7 +4936,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>CENTRO DE ABASTECIMIENTO (M)</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -4946,12 +4946,12 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>JOSÉ HERMINIO BARRIENTOS BARRIENTOS</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
+          <t>7.560.370-3</t>
         </is>
       </c>
       <c r="K74" t="inlineStr"/>
@@ -4961,13 +4961,13 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>4964.93</v>
+        <v>1530.06</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>3166-36-CM26</t>
+          <t>3166-35-CM26</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4997,7 +4997,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>CENTRO DE ABASTECIMIENTO (M)</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5007,12 +5007,12 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>77.346.435-9</t>
         </is>
       </c>
       <c r="K75" t="inlineStr"/>
@@ -5022,13 +5022,13 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>4150.45</v>
+        <v>4964.93</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>3166-33-CM26</t>
+          <t>3166-36-CM26</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5058,7 +5058,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>CENTRO DE ABASTECIMIENTO (M)</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5068,12 +5068,12 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>JOSÉ HERMINIO BARRIENTOS BARRIENTOS</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>7.560.370-3</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K76" t="inlineStr"/>
@@ -5083,7 +5083,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>1530.06</v>
+        <v>4150.45</v>
       </c>
     </row>
     <row r="77">
@@ -5119,7 +5119,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>CENTRO DE ABASTECIMIENTO (M)</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5302,7 +5302,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>CENTRO DE ABASTECIMIENTO (M)</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5353,7 +5353,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -5516,7 +5516,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2099-61-CM26</t>
+          <t>2099-60-CM26</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>IVÁN DAMIR STIPICIC MATIC</t>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>8.588.169-8</t>
+          <t>78.307.990-9</t>
         </is>
       </c>
       <c r="K84" t="inlineStr"/>
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>1380.44</v>
+        <v>3159.88</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2099-60-CM26</t>
+          <t>2099-61-CM26</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5617,12 +5617,12 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+          <t>IVÁN DAMIR STIPICIC MATIC</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>78.307.990-9</t>
+          <t>8.588.169-8</t>
         </is>
       </c>
       <c r="K85" t="inlineStr"/>
@@ -5632,7 +5632,7 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>3159.88</v>
+        <v>1380.44</v>
       </c>
     </row>
     <row r="86">
@@ -5821,7 +5821,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>3268-119-CM26</t>
+          <t>3595-101-CM26</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5846,12 +5846,12 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>61.103.021-5</t>
+          <t>69.251.400-9</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>IVª Brigada Aérea</t>
+          <t>ILUSTRE MUNICIPALIDAD DE RIO VERDE</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -5861,12 +5861,12 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+          <t>ANTALIS CHILE LIMITADA</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>78.307.990-9</t>
+          <t>77.305.910-1</t>
         </is>
       </c>
       <c r="K89" t="inlineStr"/>
@@ -5876,13 +5876,13 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>1260.44</v>
+        <v>1043.13</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>3595-101-CM26</t>
+          <t>874750-90-CM26</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -5907,12 +5907,12 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>69.251.400-9</t>
+          <t>61.607.903-4</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE RIO VERDE</t>
+          <t>SERVICIO DE SALUD MAGALLANES</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -5922,12 +5922,12 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>ANTALIS CHILE LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>77.305.910-1</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K90" t="inlineStr"/>
@@ -5937,13 +5937,13 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>1043.13</v>
+        <v>1550.17</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>874750-90-CM26</t>
+          <t>3268-119-CM26</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>61.607.903-4</t>
+          <t>61.103.021-5</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PORVENIR</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -5983,12 +5983,12 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>78.307.990-9</t>
         </is>
       </c>
       <c r="K91" t="inlineStr"/>
@@ -5998,7 +5998,7 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>1550.17</v>
+        <v>1260.44</v>
       </c>
     </row>
     <row r="92">
@@ -6126,7 +6126,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>3638-113-CM26</t>
+          <t>1347-8-CM26</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6146,17 +6146,17 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>69.250.300-7</t>
+          <t>61.002.492-0</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>I.MUNICIPALIDAD DE PORVENIR</t>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -6181,13 +6181,13 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>2703.35</v>
+        <v>1524.42</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>3638-112-CM26</t>
+          <t>1347-9-CM26</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6207,17 +6207,17 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>69.250.300-7</t>
+          <t>61.002.492-0</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>I.MUNICIPALIDAD DE PORVENIR</t>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>JOSÉ HERMINIO BARRIENTOS BARRIENTOS</t>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>7.560.370-3</t>
+          <t>78.307.990-9</t>
         </is>
       </c>
       <c r="K95" t="inlineStr"/>
@@ -6242,13 +6242,13 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>784.59</v>
+        <v>929.36</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>1347-8-CM26</t>
+          <t>1347-10-CM26</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6278,7 +6278,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>REG CIVIL E IDENT PUNTA ARENAS</t>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -6288,12 +6288,12 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>IVÁN DAMIR STIPICIC MATIC</t>
+          <t>LIBRERIA</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>8.588.169-8</t>
+          <t>76.567.094-2</t>
         </is>
       </c>
       <c r="K96" t="inlineStr"/>
@@ -6303,13 +6303,13 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>1524.42</v>
+        <v>8746.74</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>1347-9-CM26</t>
+          <t>3638-112-CM26</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6329,17 +6329,17 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>61.002.492-0</t>
+          <t>69.250.300-7</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>REG CIVIL E IDENT PUNTA ARENAS</t>
+          <t>I.MUNICIPALIDAD DE PORVENIR</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -6349,12 +6349,12 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+          <t>JOSÉ HERMINIO BARRIENTOS BARRIENTOS</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>78.307.990-9</t>
+          <t>7.560.370-3</t>
         </is>
       </c>
       <c r="K97" t="inlineStr"/>
@@ -6364,13 +6364,13 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>929.36</v>
+        <v>784.59</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>1347-10-CM26</t>
+          <t>3638-113-CM26</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6390,17 +6390,17 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>61.002.492-0</t>
+          <t>69.250.300-7</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>REG CIVIL E IDENT PUNTA ARENAS</t>
+          <t>I.MUNICIPALIDAD DE PORVENIR</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -6410,12 +6410,12 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>LIBRERIA</t>
+          <t>IVÁN DAMIR STIPICIC MATIC</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>76.567.094-2</t>
+          <t>8.588.169-8</t>
         </is>
       </c>
       <c r="K98" t="inlineStr"/>
@@ -6425,7 +6425,7 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>8746.74</v>
+        <v>2703.35</v>
       </c>
     </row>
     <row r="99">
@@ -6522,7 +6522,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Jefatura Adm. y Log. del Campo Militar Austral</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -6888,7 +6888,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PORVENIR</t>
+          <t>SERVICIO DE SALUD MAGALLANES</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -7010,7 +7010,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>DEPTO BIENESTAR SOCIAL (M) 3RA ZONA NAVA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -7071,7 +7071,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACION TECNICA ESTATAL DE MAGALLANES</t>
+          <t>CENTRO DE FORMACION TECNICA ESTATAL DE MAGALLANES Y ANTARTICA CHILENA</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -7132,7 +7132,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACION TECNICA ESTATAL DE MAGALLANES</t>
+          <t>CENTRO DE FORMACION TECNICA ESTATAL DE MAGALLANES Y ANTARTICA CHILENA</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -7224,7 +7224,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>1890-9-CM26</t>
+          <t>1233613-907-CM26</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -7249,12 +7249,12 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>61.941.900-6</t>
+          <t>61.980.960-2</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>DEFENSORIA PENAL PUBLICA</t>
+          <t>Servicio Local de Educación Pública Magallanes</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K112" t="inlineStr"/>
@@ -7279,13 +7279,13 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>808.77</v>
+        <v>1124.32</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>1233613-907-CM26</t>
+          <t>1890-9-CM26</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>61.980.960-2</t>
+          <t>61.941.900-6</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Magallanes</t>
+          <t>DEFENSORIA PENAL PUBLICA</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -7325,12 +7325,12 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.346.435-9</t>
         </is>
       </c>
       <c r="K113" t="inlineStr"/>
@@ -7340,7 +7340,7 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>1124.32</v>
+        <v>808.77</v>
       </c>
     </row>
     <row r="114">
@@ -7376,7 +7376,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -7559,7 +7559,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Ministerio Publico</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -7671,7 +7671,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -7681,7 +7681,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Ministerio Publico</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -7742,7 +7742,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Jefatura Adm. y Log. del Campo Militar Austral</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -7925,7 +7925,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Ministerio de Vivienda y Urbanismo</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -8169,7 +8169,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>HOSPITAL NAVAL CIRUJANO GUZMAN DE MAGALL</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -8840,7 +8840,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PORVENIR</t>
+          <t>SERVICIO DE SALUD MAGALLANES</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -8901,7 +8901,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>IVª Brigada Aérea</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -8962,7 +8962,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>CENTRAL ODONTOLOGICA MAGALLANES</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -9013,7 +9013,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -9023,7 +9023,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>DEPTO BIENESTAR SOCIAL (M) 3RA ZONA NAVA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -9659,6 +9659,555 @@
       </c>
       <c r="M151" s="2" t="n">
         <v>1105.09</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>3130-6503-CM26</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>61.102.029-5</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>78.307.990-9</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr"/>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M152" s="2" t="n">
+        <v>805.64</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>5394-536-CM26</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>71.133.700-8</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE MAGALLANES</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>LIBRERIA</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>76.567.094-2</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr"/>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M153" s="2" t="n">
+        <v>2993.43</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>3268-649-CM26</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>61.103.021-5</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>78.307.990-9</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr"/>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M154" s="2" t="n">
+        <v>1184.68</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>4627-16-CM26</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>61.502.000-1</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>DIRECCION DEL TRABAJO</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>LIBRERIA</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>76.567.094-2</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr"/>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M155" s="2" t="n">
+        <v>2895.53</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>1237328-503-CM26</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>70.931.900-0</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>CORP MUNICIPAL DE PUNTA ARENAS PARA LA EDUCACION SALUD Y AT AL MENOR</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>IVÁN DAMIR STIPICIC MATIC</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>8.588.169-8</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr"/>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M156" s="2" t="n">
+        <v>2629.57</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>1057402-9542-CM26</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>61.607.901-8</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>78.307.990-9</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr"/>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M157" s="2" t="n">
+        <v>796</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>1208985-105-CM26</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>62.000.890-7</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>78.307.990-9</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr"/>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M158" s="2" t="n">
+        <v>1254.16</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>1878-38-CM26</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>60.704.000-1</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE TURISMO</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>78.307.990-9</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr"/>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M159" s="2" t="n">
+        <v>1920.1</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>1057402-10385-CM26</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>61.607.901-8</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>78.307.990-9</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr"/>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M160" s="2" t="n">
+        <v>766.55</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/articulos-de-escritorio-y-papeleria/magallanes.xlsx
+++ b/docs/oc-regiones/articulos-de-escritorio-y-papeleria/magallanes.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M243"/>
+  <dimension ref="A1:M251"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1709,7 +1709,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1000813-49-CM25</t>
+          <t>1000813-48-CM25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1764,13 +1764,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>1824.14</v>
+        <v>2719</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1000813-48-CM25</t>
+          <t>1000813-49-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1825,7 +1825,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>2719</v>
+        <v>1824.14</v>
       </c>
     </row>
     <row r="23">
@@ -2408,7 +2408,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>874750-88-CM25</t>
+          <t>874750-90-CM25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2448,28 +2448,32 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>IVÁN DAMIR STIPICIC MATIC</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>8.588.169-8</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr"/>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>761.49</v>
+        <v>804.55</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>874750-90-CM25</t>
+          <t>3187-102-CM25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2494,12 +2498,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>61.607.903-4</t>
+          <t>61.102.041-4</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD MAGALLANES</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2509,17 +2513,17 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>78.307.990-9</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2528,13 +2532,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>804.55</v>
+        <v>776.34</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>3187-102-CM25</t>
+          <t>874750-88-CM25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2559,12 +2563,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>61.102.041-4</t>
+          <t>61.607.903-4</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>SERVICIO DE SALUD MAGALLANES</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2574,26 +2578,22 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+          <t>IVÁN DAMIR STIPICIC MATIC</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>78.307.990-9</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>8.588.169-8</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>776.34</v>
+        <v>761.49</v>
       </c>
     </row>
     <row r="35">
@@ -2790,7 +2790,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>5338-103-CM25</t>
+          <t>1057402-18944-CM25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2815,12 +2815,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>71.133.700-8</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE MAGALLANES</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2849,13 +2849,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>2799.08</v>
+        <v>11721.65</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1057402-18944-CM25</t>
+          <t>1057402-18951-CM25</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2895,32 +2895,28 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+          <t>LIBRERIA</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>78.307.990-9</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.567.094-2</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>11721.65</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1057402-18951-CM25</t>
+          <t>5338-103-CM25</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2945,12 +2941,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>71.133.700-8</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>UNIVERSIDAD DE MAGALLANES</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2960,22 +2956,26 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>LIBRERIA</t>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>76.567.094-2</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr"/>
+          <t>78.307.990-9</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>1746</v>
+        <v>2799.08</v>
       </c>
     </row>
     <row r="41">
@@ -4188,7 +4188,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>1057402-22880-CM25</t>
+          <t>1057402-22938-CM25</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4228,32 +4228,28 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+          <t>LIBRERIA</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>78.307.990-9</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.567.094-2</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>1547.57</v>
+        <v>914.64</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1057402-22938-CM25</t>
+          <t>1057402-23100-CM25</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4293,28 +4289,32 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>LIBRERIA</t>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>76.567.094-2</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr"/>
+          <t>78.307.990-9</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>914.64</v>
+        <v>5099.51</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1057402-23100-CM25</t>
+          <t>1057402-22880-CM25</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4373,7 +4373,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>5099.51</v>
+        <v>1547.57</v>
       </c>
     </row>
     <row r="63">
@@ -4814,7 +4814,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>1057402-24232-CM25</t>
+          <t>1057402-24231-CM25</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4854,32 +4854,28 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+          <t>LIBRERIA</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>78.307.990-9</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.567.094-2</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>811.23</v>
+        <v>5795.97</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>1057402-24231-CM25</t>
+          <t>1057402-24232-CM25</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4919,22 +4915,26 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>LIBRERIA</t>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>76.567.094-2</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr"/>
+          <t>78.307.990-9</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>5795.97</v>
+        <v>811.23</v>
       </c>
     </row>
     <row r="72">
@@ -5444,7 +5444,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>874750-243-CM25</t>
+          <t>874750-242-CM25</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5484,28 +5484,32 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>IVÁN DAMIR STIPICIC MATIC</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>8.588.169-8</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr"/>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>2100.84</v>
+        <v>823.3</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>874750-244-CM25</t>
+          <t>874750-243-CM25</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5545,12 +5549,12 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>LIBRERIA</t>
+          <t>IVÁN DAMIR STIPICIC MATIC</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>76.567.094-2</t>
+          <t>8.588.169-8</t>
         </is>
       </c>
       <c r="K81" t="inlineStr"/>
@@ -5560,13 +5564,13 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>1905.13</v>
+        <v>2100.84</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>874750-242-CM25</t>
+          <t>874750-244-CM25</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5606,26 +5610,22 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>LIBRERIA</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>Antofagasta</t>
-        </is>
-      </c>
+          <t>76.567.094-2</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr"/>
       <c r="L82" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>823.3</v>
+        <v>1905.13</v>
       </c>
     </row>
     <row r="83">
@@ -6586,7 +6586,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>1540-2041-CM25</t>
+          <t>1038-226-CM25</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6611,12 +6611,12 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>61.607.904-2</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PTO NATALES</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -6626,32 +6626,28 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>LIBRERIA</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
-        </is>
-      </c>
-      <c r="K98" t="inlineStr">
-        <is>
-          <t>Antofagasta</t>
-        </is>
-      </c>
+          <t>76.567.094-2</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr"/>
       <c r="L98" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>5612.03</v>
+        <v>731.7</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>1038-226-CM25</t>
+          <t>1540-2041-CM25</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6676,12 +6672,12 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.607.904-2</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PTO NATALES</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -6691,22 +6687,26 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>LIBRERIA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>76.567.094-2</t>
-        </is>
-      </c>
-      <c r="K99" t="inlineStr"/>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L99" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>731.7</v>
+        <v>5612.03</v>
       </c>
     </row>
     <row r="100">
@@ -6777,7 +6777,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>5394-567-CM25</t>
+          <t>5147-278-CM25</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6802,12 +6802,12 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>71.133.700-8</t>
+          <t>69.251.600-1</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE MAGALLANES</t>
+          <t>ILUSTRE MUNICIPALIDAD DE TIMAUKEL</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -6832,13 +6832,13 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>2357.43</v>
+        <v>2552.1</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>5147-278-CM25</t>
+          <t>5394-567-CM25</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -6863,12 +6863,12 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>69.251.600-1</t>
+          <t>71.133.700-8</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE TIMAUKEL</t>
+          <t>UNIVERSIDAD DE MAGALLANES</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -6893,7 +6893,7 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>2552.1</v>
+        <v>2357.43</v>
       </c>
     </row>
     <row r="103">
@@ -7208,7 +7208,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>874750-435-CM25</t>
+          <t>5147-298-CM25</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -7228,17 +7228,17 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>61.607.903-4</t>
+          <t>69.251.600-1</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD MAGALLANES</t>
+          <t>ILUSTRE MUNICIPALIDAD DE TIMAUKEL</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -7248,12 +7248,12 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>MARANGUNIC HERMANOS LIMITADA</t>
+          <t>IVÁN DAMIR STIPICIC MATIC</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>80.586.800-7</t>
+          <t>8.588.169-8</t>
         </is>
       </c>
       <c r="K108" t="inlineStr"/>
@@ -7263,7 +7263,7 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>720.97</v>
+        <v>725.21</v>
       </c>
     </row>
     <row r="109">
@@ -7330,7 +7330,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>5147-298-CM25</t>
+          <t>874750-435-CM25</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -7350,17 +7350,17 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>69.251.600-1</t>
+          <t>61.607.903-4</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE TIMAUKEL</t>
+          <t>SERVICIO DE SALUD MAGALLANES</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -7370,12 +7370,12 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>IVÁN DAMIR STIPICIC MATIC</t>
+          <t>MARANGUNIC HERMANOS LIMITADA</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>8.588.169-8</t>
+          <t>80.586.800-7</t>
         </is>
       </c>
       <c r="K110" t="inlineStr"/>
@@ -7385,13 +7385,13 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>725.21</v>
+        <v>720.97</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>1057402-36793-CM25</t>
+          <t>874750-440-CM25</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>61.607.903-4</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>SERVICIO DE SALUD MAGALLANES</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -7431,32 +7431,28 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+          <t>IVÁN DAMIR STIPICIC MATIC</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>78.307.990-9</t>
-        </is>
-      </c>
-      <c r="K111" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>8.588.169-8</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr"/>
       <c r="L111" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>723.41</v>
+        <v>727.3099999999999</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>874750-440-CM25</t>
+          <t>1057402-36793-CM25</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -7481,12 +7477,12 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>61.607.903-4</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD MAGALLANES</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -7496,22 +7492,26 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>IVÁN DAMIR STIPICIC MATIC</t>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>8.588.169-8</t>
-        </is>
-      </c>
-      <c r="K112" t="inlineStr"/>
+          <t>78.307.990-9</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L112" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>727.3099999999999</v>
+        <v>723.41</v>
       </c>
     </row>
     <row r="113">
@@ -7765,7 +7765,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>1109692-269-CM25</t>
+          <t>1988-74-CM25</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -7785,17 +7785,17 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>62.000.760-9</t>
+          <t>60.701.003-K</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACION TECNICA ESTATAL DE MAGALLANES Y ANTARTICA CHILENA</t>
+          <t>SERV NACIONAL DE PESCA</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -7824,13 +7824,13 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>1227.62</v>
+        <v>745.76</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>1988-74-CM25</t>
+          <t>1109692-269-CM25</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -7850,17 +7850,17 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>60.701.003-K</t>
+          <t>62.000.760-9</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>SERV NACIONAL DE PESCA</t>
+          <t>CENTRO DE FORMACION TECNICA ESTATAL DE MAGALLANES Y ANTARTICA CHILENA</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -7889,7 +7889,7 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>745.76</v>
+        <v>1227.62</v>
       </c>
     </row>
     <row r="119">
@@ -9996,7 +9996,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>5338-31-CM26</t>
+          <t>3617-2-CM26</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -10021,12 +10021,12 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>71.133.700-8</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE MAGALLANES</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -10036,17 +10036,17 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>78.307.990-9</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
@@ -10055,13 +10055,13 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>14311.5</v>
+        <v>1392.72</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>3617-2-CM26</t>
+          <t>5338-31-CM26</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -10086,12 +10086,12 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>71.133.700-8</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>UNIVERSIDAD DE MAGALLANES</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -10101,17 +10101,17 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>78.307.990-9</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
@@ -10120,7 +10120,7 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>1392.72</v>
+        <v>14311.5</v>
       </c>
     </row>
     <row r="154">
@@ -10321,7 +10321,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>3166-33-CM26</t>
+          <t>3166-36-CM26</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -10361,22 +10361,26 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>JOSÉ HERMINIO BARRIENTOS BARRIENTOS</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>7.560.370-3</t>
-        </is>
-      </c>
-      <c r="K157" t="inlineStr"/>
+          <t>76.710.414-6</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L157" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>1530.06</v>
+        <v>4150.45</v>
       </c>
     </row>
     <row r="158">
@@ -10447,7 +10451,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>3166-36-CM26</t>
+          <t>3166-33-CM26</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -10487,26 +10491,22 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>JOSÉ HERMINIO BARRIENTOS BARRIENTOS</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
-        </is>
-      </c>
-      <c r="K159" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>7.560.370-3</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr"/>
       <c r="L159" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>4150.45</v>
+        <v>1530.06</v>
       </c>
     </row>
     <row r="160">
@@ -10967,7 +10967,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2099-60-CM26</t>
+          <t>2099-61-CM26</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -11007,32 +11007,28 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+          <t>IVÁN DAMIR STIPICIC MATIC</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>78.307.990-9</t>
-        </is>
-      </c>
-      <c r="K167" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>8.588.169-8</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr"/>
       <c r="L167" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>3159.88</v>
+        <v>1380.44</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2099-61-CM26</t>
+          <t>2099-60-CM26</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -11072,22 +11068,26 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>IVÁN DAMIR STIPICIC MATIC</t>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>8.588.169-8</t>
-        </is>
-      </c>
-      <c r="K168" t="inlineStr"/>
+          <t>78.307.990-9</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L168" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>1380.44</v>
+        <v>3159.88</v>
       </c>
     </row>
     <row r="169">
@@ -11276,7 +11276,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>874750-90-CM26</t>
+          <t>3268-119-CM26</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -11301,12 +11301,12 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>61.607.903-4</t>
+          <t>61.103.021-5</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD MAGALLANES</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -11316,17 +11316,17 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>78.307.990-9</t>
         </is>
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L172" t="inlineStr">
@@ -11335,13 +11335,13 @@
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>1550.17</v>
+        <v>1260.44</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>3595-101-CM26</t>
+          <t>874750-90-CM26</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -11366,12 +11366,12 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>69.251.400-9</t>
+          <t>61.607.903-4</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE RIO VERDE</t>
+          <t>SERVICIO DE SALUD MAGALLANES</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -11381,17 +11381,17 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>ANTALIS CHILE LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>77.305.910-1</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
@@ -11400,13 +11400,13 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>1043.13</v>
+        <v>1550.17</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>3268-119-CM26</t>
+          <t>3595-101-CM26</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -11431,12 +11431,12 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>61.103.021-5</t>
+          <t>69.251.400-9</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+          <t>ILUSTRE MUNICIPALIDAD DE RIO VERDE</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -11446,12 +11446,12 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+          <t>ANTALIS CHILE LIMITADA</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>78.307.990-9</t>
+          <t>77.305.910-1</t>
         </is>
       </c>
       <c r="K174" t="inlineStr">
@@ -11465,13 +11465,13 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>1260.44</v>
+        <v>1043.13</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>1162-40-CM26</t>
+          <t>1057402-2609-CM26</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -11491,17 +11491,17 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -11530,13 +11530,13 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>798.0599999999999</v>
+        <v>918.0599999999999</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>1057402-2609-CM26</t>
+          <t>1162-40-CM26</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -11556,17 +11556,17 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -11595,13 +11595,13 @@
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>918.0599999999999</v>
+        <v>798.0599999999999</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>1347-8-CM26</t>
+          <t>1347-9-CM26</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -11641,28 +11641,32 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>IVÁN DAMIR STIPICIC MATIC</t>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>8.588.169-8</t>
-        </is>
-      </c>
-      <c r="K177" t="inlineStr"/>
+          <t>78.307.990-9</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L177" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>1524.42</v>
+        <v>929.36</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>1347-9-CM26</t>
+          <t>1347-8-CM26</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -11702,32 +11706,28 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+          <t>IVÁN DAMIR STIPICIC MATIC</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>78.307.990-9</t>
-        </is>
-      </c>
-      <c r="K178" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>8.588.169-8</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr"/>
       <c r="L178" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>929.36</v>
+        <v>1524.42</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>1347-10-CM26</t>
+          <t>3638-113-CM26</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -11747,17 +11747,17 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>61.002.492-0</t>
+          <t>69.250.300-7</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
+          <t>I.MUNICIPALIDAD DE PORVENIR</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -11767,12 +11767,12 @@
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>LIBRERIA</t>
+          <t>IVÁN DAMIR STIPICIC MATIC</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>76.567.094-2</t>
+          <t>8.588.169-8</t>
         </is>
       </c>
       <c r="K179" t="inlineStr"/>
@@ -11782,7 +11782,7 @@
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>8746.74</v>
+        <v>2703.35</v>
       </c>
     </row>
     <row r="180">
@@ -11849,7 +11849,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>3638-113-CM26</t>
+          <t>1347-10-CM26</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -11869,17 +11869,17 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>69.250.300-7</t>
+          <t>61.002.492-0</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>I.MUNICIPALIDAD DE PORVENIR</t>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -11889,12 +11889,12 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>IVÁN DAMIR STIPICIC MATIC</t>
+          <t>LIBRERIA</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>8.588.169-8</t>
+          <t>76.567.094-2</t>
         </is>
       </c>
       <c r="K181" t="inlineStr"/>
@@ -11904,7 +11904,7 @@
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>2703.35</v>
+        <v>8746.74</v>
       </c>
     </row>
     <row r="182">
@@ -12410,7 +12410,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>5147-97-CM26</t>
+          <t>3241-83-CM26</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -12430,17 +12430,17 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>69.251.600-1</t>
+          <t>61.102.028-7</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE TIMAUKEL</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -12450,28 +12450,32 @@
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>IVÁN DAMIR STIPICIC MATIC</t>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>8.588.169-8</t>
-        </is>
-      </c>
-      <c r="K190" t="inlineStr"/>
+          <t>78.307.990-9</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L190" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>2761.43</v>
+        <v>917.9299999999999</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>3241-83-CM26</t>
+          <t>1109692-96-CM26</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -12496,12 +12500,12 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>61.102.028-7</t>
+          <t>62.000.760-9</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>CENTRO DE FORMACION TECNICA ESTATAL DE MAGALLANES Y ANTARTICA CHILENA</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -12511,32 +12515,28 @@
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+          <t>JOSÉ HERMINIO BARRIENTOS BARRIENTOS</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>78.307.990-9</t>
-        </is>
-      </c>
-      <c r="K191" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>7.560.370-3</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr"/>
       <c r="L191" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>917.9299999999999</v>
+        <v>832.89</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>1109692-96-CM26</t>
+          <t>5147-97-CM26</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -12556,17 +12556,17 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>62.000.760-9</t>
+          <t>69.251.600-1</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACION TECNICA ESTATAL DE MAGALLANES Y ANTARTICA CHILENA</t>
+          <t>ILUSTRE MUNICIPALIDAD DE TIMAUKEL</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -12576,12 +12576,12 @@
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>JOSÉ HERMINIO BARRIENTOS BARRIENTOS</t>
+          <t>IVÁN DAMIR STIPICIC MATIC</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>7.560.370-3</t>
+          <t>8.588.169-8</t>
         </is>
       </c>
       <c r="K192" t="inlineStr"/>
@@ -12591,7 +12591,7 @@
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>832.89</v>
+        <v>2761.43</v>
       </c>
     </row>
     <row r="193">
@@ -13296,7 +13296,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>855-74-CM26</t>
+          <t>1038-109-CM26</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -13321,12 +13321,12 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -13355,13 +13355,13 @@
         </is>
       </c>
       <c r="M204" s="2" t="n">
-        <v>6028.79</v>
+        <v>1642.73</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>1038-109-CM26</t>
+          <t>855-74-CM26</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -13386,12 +13386,12 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -13420,7 +13420,7 @@
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>1642.73</v>
+        <v>6028.79</v>
       </c>
     </row>
     <row r="206">
@@ -13869,7 +13869,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>855-102-CM26</t>
+          <t>855-101-CM26</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -13889,7 +13889,7 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
@@ -13909,32 +13909,28 @@
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>IVÁN DAMIR STIPICIC MATIC</t>
         </is>
       </c>
       <c r="J213" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
-        </is>
-      </c>
-      <c r="K213" t="inlineStr">
-        <is>
-          <t>Antofagasta</t>
-        </is>
-      </c>
+          <t>8.588.169-8</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr"/>
       <c r="L213" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>3342.38</v>
+        <v>5198.91</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>855-101-CM26</t>
+          <t>855-99-CM26</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -13989,13 +13985,13 @@
         </is>
       </c>
       <c r="M214" s="2" t="n">
-        <v>5198.91</v>
+        <v>2502.07</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>855-99-CM26</t>
+          <t>855-100-CM26</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -14015,7 +14011,7 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
@@ -14035,28 +14031,32 @@
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>IVÁN DAMIR STIPICIC MATIC</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J215" t="inlineStr">
         <is>
-          <t>8.588.169-8</t>
-        </is>
-      </c>
-      <c r="K215" t="inlineStr"/>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L215" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>2502.07</v>
+        <v>1552.99</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>855-100-CM26</t>
+          <t>855-102-CM26</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -14115,7 +14115,7 @@
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>1552.99</v>
+        <v>3342.38</v>
       </c>
     </row>
     <row r="217">
@@ -15389,7 +15389,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>3268-649-CM26</t>
+          <t>4627-16-CM26</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -15414,12 +15414,12 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>61.103.021-5</t>
+          <t>61.502.000-1</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+          <t>DIRECCION DEL TRABAJO</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
@@ -15429,32 +15429,28 @@
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+          <t>LIBRERIA</t>
         </is>
       </c>
       <c r="J237" t="inlineStr">
         <is>
-          <t>78.307.990-9</t>
-        </is>
-      </c>
-      <c r="K237" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.567.094-2</t>
+        </is>
+      </c>
+      <c r="K237" t="inlineStr"/>
       <c r="L237" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M237" s="2" t="n">
-        <v>1184.68</v>
+        <v>2895.53</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>4627-16-CM26</t>
+          <t>3268-649-CM26</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -15479,12 +15475,12 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>61.502.000-1</t>
+          <t>61.103.021-5</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>DIRECCION DEL TRABAJO</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -15494,28 +15490,32 @@
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>LIBRERIA</t>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
         </is>
       </c>
       <c r="J238" t="inlineStr">
         <is>
-          <t>76.567.094-2</t>
-        </is>
-      </c>
-      <c r="K238" t="inlineStr"/>
+          <t>78.307.990-9</t>
+        </is>
+      </c>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L238" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M238" s="2" t="n">
-        <v>2895.53</v>
+        <v>1184.68</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>1237328-503-CM26</t>
+          <t>1057402-9542-CM26</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -15535,17 +15535,17 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>70.931.900-0</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE PUNTA ARENAS PARA LA EDUCACION SALUD Y AT AL MENOR</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -15555,28 +15555,32 @@
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t>IVÁN DAMIR STIPICIC MATIC</t>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
         </is>
       </c>
       <c r="J239" t="inlineStr">
         <is>
-          <t>8.588.169-8</t>
-        </is>
-      </c>
-      <c r="K239" t="inlineStr"/>
+          <t>78.307.990-9</t>
+        </is>
+      </c>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L239" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M239" s="2" t="n">
-        <v>2629.57</v>
+        <v>796</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>1057402-9542-CM26</t>
+          <t>1237328-503-CM26</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -15601,12 +15605,12 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>70.931.900-0</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>CORP MUNICIPAL DE PUNTA ARENAS PARA LA EDUCACION SALUD Y AT AL MENOR</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
@@ -15616,26 +15620,22 @@
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+          <t>IVÁN DAMIR STIPICIC MATIC</t>
         </is>
       </c>
       <c r="J240" t="inlineStr">
         <is>
-          <t>78.307.990-9</t>
-        </is>
-      </c>
-      <c r="K240" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>8.588.169-8</t>
+        </is>
+      </c>
+      <c r="K240" t="inlineStr"/>
       <c r="L240" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M240" s="2" t="n">
-        <v>796</v>
+        <v>2629.57</v>
       </c>
     </row>
     <row r="241">
@@ -15661,7 +15661,7 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
@@ -15831,6 +15831,510 @@
       </c>
       <c r="M243" s="2" t="n">
         <v>766.55</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>1208985-116-CM26</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>62.000.890-7</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+        </is>
+      </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+        </is>
+      </c>
+      <c r="J244" t="inlineStr">
+        <is>
+          <t>78.307.990-9</t>
+        </is>
+      </c>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L244" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M244" s="2" t="n">
+        <v>746.1799999999999</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>855-212-CM26</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>70.072.600-2</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>JOSÉ HERMINIO BARRIENTOS BARRIENTOS</t>
+        </is>
+      </c>
+      <c r="J245" t="inlineStr">
+        <is>
+          <t>7.560.370-3</t>
+        </is>
+      </c>
+      <c r="K245" t="inlineStr"/>
+      <c r="L245" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M245" s="2" t="n">
+        <v>9149.43</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>855-214-CM26</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>70.072.600-2</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>JOSÉ HERMINIO BARRIENTOS BARRIENTOS</t>
+        </is>
+      </c>
+      <c r="J246" t="inlineStr">
+        <is>
+          <t>7.560.370-3</t>
+        </is>
+      </c>
+      <c r="K246" t="inlineStr"/>
+      <c r="L246" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M246" s="2" t="n">
+        <v>1571.6</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>855-215-CM26</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>70.072.600-2</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>MARANGUNIC HERMANOS LIMITADA</t>
+        </is>
+      </c>
+      <c r="J247" t="inlineStr">
+        <is>
+          <t>80.586.800-7</t>
+        </is>
+      </c>
+      <c r="K247" t="inlineStr"/>
+      <c r="L247" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M247" s="2" t="n">
+        <v>2581.43</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>697-317-CM26</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>60.605.000-3</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>INSTITUTO ANTARTICO CHILENO</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+        </is>
+      </c>
+      <c r="J248" t="inlineStr">
+        <is>
+          <t>78.307.990-9</t>
+        </is>
+      </c>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L248" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M248" s="2" t="n">
+        <v>1222.24</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>1540-2284-CM26</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>61.607.904-2</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PTO NATALES</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+        </is>
+      </c>
+      <c r="J249" t="inlineStr">
+        <is>
+          <t>78.307.990-9</t>
+        </is>
+      </c>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L249" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M249" s="2" t="n">
+        <v>2746.58</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>2019-84-CM26</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>60.511.122-k</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE ÚLTIMA ESPERANZA</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>JOSÉ HERMINIO BARRIENTOS BARRIENTOS</t>
+        </is>
+      </c>
+      <c r="J250" t="inlineStr">
+        <is>
+          <t>7.560.370-3</t>
+        </is>
+      </c>
+      <c r="K250" t="inlineStr"/>
+      <c r="L250" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M250" s="2" t="n">
+        <v>1058.6</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>1540-2295-CM26</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>61.607.904-2</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PTO NATALES</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+        </is>
+      </c>
+      <c r="J251" t="inlineStr">
+        <is>
+          <t>78.307.990-9</t>
+        </is>
+      </c>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L251" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M251" s="2" t="n">
+        <v>789.1900000000001</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/articulos-de-escritorio-y-papeleria/magallanes.xlsx
+++ b/docs/oc-regiones/articulos-de-escritorio-y-papeleria/magallanes.xlsx
@@ -15921,7 +15921,7 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
